--- a/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0002T0006Z000C1N7_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0002T0006Z000C1N7_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>6.964086221099024</v>
+        <v>1.131664010928592</v>
       </c>
       <c r="D2" t="n">
-        <v>10.05224578047396</v>
+        <v>1.633489939327019</v>
       </c>
       <c r="E2" t="n">
-        <v>2.694309724165889</v>
+        <v>0.437825330176957</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9988096410398901</v>
+        <v>0.1623065666689821</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>12.3527056694308</v>
+        <v>2.007314671282506</v>
       </c>
       <c r="D3" t="n">
-        <v>12.04986506255374</v>
+        <v>1.958103072664983</v>
       </c>
       <c r="E3" t="n">
-        <v>2.694309724165889</v>
+        <v>0.437825330176957</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9988096410398901</v>
+        <v>0.1623065666689821</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
